--- a/签到条模板.xlsx
+++ b/签到条模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="签到条模板" sheetId="1" r:id="rId1"/>
@@ -27,10 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>XX活动签到表</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>姓名</t>
   </si>
@@ -431,49 +428,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -615,7 +575,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -627,34 +587,34 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -739,23 +699,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1291,8 +1242,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="3"/>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="3"/>
   <cols>
     <col min="3" max="3" width="17.875" customWidth="1"/>
   </cols>
@@ -1301,66 +1252,55 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3"/>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="4"/>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="4" t="s">
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D4" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
